--- a/liaisons_Super_Constellation/Reseau_Nordair_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Nordair_L1049_sourced.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Québec &amp; Arctique (illustratif)" sheetId="1" r:id="rId1"/>
+    <sheet name="Lignes DC-6" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
         <v>ND 201</v>
       </c>
       <c r="B2" t="str">
-        <v>Liaison de l'Ungava</v>
+        <v>Baffin (Cape Dyer)</v>
       </c>
       <c r="C2" t="str">
         <v>Montréal (YUL)</v>
@@ -439,13 +439,13 @@
         <v>07:30</v>
       </c>
       <c r="E2" t="str">
-        <v>Val-d'Or (09:00 / 09:45)</v>
+        <v>Frobisher Bay (12:30 / 13:30)</v>
       </c>
       <c r="F2" t="str">
-        <v>Frobisher Bay</v>
+        <v>Cape Dyer</v>
       </c>
       <c r="G2" t="str">
-        <v>14:45</v>
+        <v>15:30</v>
       </c>
       <c r="H2" t="str">
         <v>Mardi, Vendredi</v>
@@ -456,22 +456,22 @@
         <v>ND 202</v>
       </c>
       <c r="B3" t="str">
-        <v>Liaison de l'Ungava (Retour)</v>
+        <v>Baffin (Cape Dyer) (Retour)</v>
       </c>
       <c r="C3" t="str">
-        <v>Frobisher Bay</v>
+        <v>Cape Dyer</v>
       </c>
       <c r="D3" t="str">
         <v>13:00</v>
       </c>
       <c r="E3" t="str">
-        <v>Val-d'Or (18:00 / 18:45)</v>
+        <v>Frobisher Bay (15:00 / 16:00)</v>
       </c>
       <c r="F3" t="str">
         <v>Montréal (YUL)</v>
       </c>
       <c r="G3" t="str">
-        <v>20:15</v>
+        <v>21:00</v>
       </c>
       <c r="H3" t="str">
         <v>Mercredi, Samedi</v>
@@ -479,10 +479,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ND 203</v>
+        <v>ND 220</v>
       </c>
       <c r="B4" t="str">
-        <v>Navette de la Baie</v>
+        <v>Ungava (Fort Chimo)</v>
       </c>
       <c r="C4" t="str">
         <v>Montréal (YUL)</v>
@@ -491,42 +491,42 @@
         <v>08:00</v>
       </c>
       <c r="E4" t="str">
-        <v>-</v>
+        <v>Roberval (09:30 / 10:10)</v>
       </c>
       <c r="F4" t="str">
-        <v>Churchill</v>
+        <v>Fort Chimo</v>
       </c>
       <c r="G4" t="str">
-        <v>13:00</v>
+        <v>14:10</v>
       </c>
       <c r="H4" t="str">
-        <v>Jeudi</v>
+        <v>Lundi, Jeudi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ND 204</v>
+        <v>ND 221</v>
       </c>
       <c r="B5" t="str">
-        <v>Navette de la Baie (Retour)</v>
+        <v>Ungava (Fort Chimo) (Retour)</v>
       </c>
       <c r="C5" t="str">
-        <v>Churchill</v>
+        <v>Fort Chimo</v>
       </c>
       <c r="D5" t="str">
         <v>15:00</v>
       </c>
       <c r="E5" t="str">
-        <v>-</v>
+        <v>Roberval (19:00 / 19:40)</v>
       </c>
       <c r="F5" t="str">
         <v>Montréal (YUL)</v>
       </c>
       <c r="G5" t="str">
-        <v>20:00</v>
+        <v>21:10</v>
       </c>
       <c r="H5" t="str">
-        <v>Dimanche</v>
+        <v>Mardi, Vendredi</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ATTENTION : Nordair (régional québécois, fondé en 1957) a exploité DC-3/DC-4 puis Electra et 737 — PAS le L-1049. Feuillet illustratif, ENTIÈREMENT RECONSTITUÉ [R].</v>
+        <v>Sources : Nordair (Québec) a exploité des Douglas DC-4 et un DC-6 sur ses lignes arctiques (Montréal–Frobisher Bay–Cape Dyer, Montréal–Roberval–Fort Chimo) vers 1959.</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -609,7 +609,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>[R] Aucune donnée sourcée pour le L-1049 : réseau nordique reconstitué à titre illustratif.</v>
+        <v>Ligne exploitée historiquement en Douglas DC-6 ; proposée ici pour le Super Constellation L-1049, appareil de même catégorie (quadrimoteur à pistons long-courrier).</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -635,7 +635,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+        <v>[R] Reconstitué : numéros de vol et horaires — non issus d'un timetable original.</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -661,33 +661,59 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>